--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/87.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/0_fold/87.xlsx
@@ -426,13 +426,13 @@
         <v>-4.20912274501711</v>
       </c>
       <c r="E2">
-        <v>-18.6798260326016</v>
+        <v>-16.5239101270299</v>
       </c>
       <c r="F2">
-        <v>-2.135014410405286</v>
+        <v>-1.261861323973426</v>
       </c>
       <c r="G2">
-        <v>-15.90777995197284</v>
+        <v>-13.3523979898465</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-3.529090560404261</v>
       </c>
       <c r="E3">
-        <v>-20.42941102241306</v>
+        <v>-17.74253606791602</v>
       </c>
       <c r="F3">
-        <v>-2.050552413281043</v>
+        <v>-1.043391846996098</v>
       </c>
       <c r="G3">
-        <v>-15.10965542536488</v>
+        <v>-12.74132425202566</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.878625310632909</v>
       </c>
       <c r="E4">
-        <v>-20.25752826297792</v>
+        <v>-19.01163638009163</v>
       </c>
       <c r="F4">
-        <v>-1.822555054436716</v>
+        <v>-0.9941578304107093</v>
       </c>
       <c r="G4">
-        <v>-15.08599164585017</v>
+        <v>-13.50051841836457</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.32549514723763</v>
       </c>
       <c r="E5">
-        <v>-20.57501051870768</v>
+        <v>-19.4792103783316</v>
       </c>
       <c r="F5">
-        <v>-1.712344913331255</v>
+        <v>-0.9773560543797268</v>
       </c>
       <c r="G5">
-        <v>-14.22675941440557</v>
+        <v>-12.81389472079203</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-1.841898690443206</v>
       </c>
       <c r="E6">
-        <v>-20.53054543242636</v>
+        <v>-20.34015932819589</v>
       </c>
       <c r="F6">
-        <v>-2.123807427812812</v>
+        <v>-1.248581766139147</v>
       </c>
       <c r="G6">
-        <v>-13.87594752470008</v>
+        <v>-12.71777634160483</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-1.422695246454521</v>
       </c>
       <c r="E7">
-        <v>-22.21438150812046</v>
+        <v>-21.27376311503923</v>
       </c>
       <c r="F7">
-        <v>-1.630549430876624</v>
+        <v>-0.9445452499222412</v>
       </c>
       <c r="G7">
-        <v>-13.30409713042853</v>
+        <v>-12.48465103527489</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-1.041352711955751</v>
       </c>
       <c r="E8">
-        <v>-22.75125474409981</v>
+        <v>-21.87473690059716</v>
       </c>
       <c r="F8">
-        <v>-1.430226998592425</v>
+        <v>-0.8629361501332395</v>
       </c>
       <c r="G8">
-        <v>-13.16329300755225</v>
+        <v>-11.6875908490578</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-0.6846758599471453</v>
       </c>
       <c r="E9">
-        <v>-22.96276617957608</v>
+        <v>-22.14223838870426</v>
       </c>
       <c r="F9">
-        <v>-2.014862203731426</v>
+        <v>-0.71130349705079</v>
       </c>
       <c r="G9">
-        <v>-13.13909623020572</v>
+        <v>-11.83630717577294</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-0.3334681940330767</v>
       </c>
       <c r="E10">
-        <v>-24.64123601357108</v>
+        <v>-23.11641277418232</v>
       </c>
       <c r="F10">
-        <v>-1.476501258447611</v>
+        <v>-0.620217874173762</v>
       </c>
       <c r="G10">
-        <v>-13.02316754651152</v>
+        <v>-10.92490736772051</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>0.01988037126851256</v>
       </c>
       <c r="E11">
-        <v>-25.31338835358157</v>
+        <v>-23.60757106505425</v>
       </c>
       <c r="F11">
-        <v>-1.090833276521828</v>
+        <v>-0.7230174404937778</v>
       </c>
       <c r="G11">
-        <v>-11.42337952011411</v>
+        <v>-10.62305844654084</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>0.3793569996826365</v>
       </c>
       <c r="E12">
-        <v>-26.71315778324851</v>
+        <v>-24.3654202471859</v>
       </c>
       <c r="F12">
-        <v>-0.6940875373184079</v>
+        <v>-0.3284022622503577</v>
       </c>
       <c r="G12">
-        <v>-11.46176529564196</v>
+        <v>-10.49544022654747</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>0.7420955742635768</v>
       </c>
       <c r="E13">
-        <v>-26.42108026670179</v>
+        <v>-26.1097159793564</v>
       </c>
       <c r="F13">
-        <v>-0.8562835315213567</v>
+        <v>-0.1850218052345969</v>
       </c>
       <c r="G13">
-        <v>-11.11394944964951</v>
+        <v>-8.971728536642518</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>1.099759133928356</v>
       </c>
       <c r="E14">
-        <v>-27.36413950727315</v>
+        <v>-26.28153986862943</v>
       </c>
       <c r="F14">
-        <v>-0.5544322485130364</v>
+        <v>0.09046751354703185</v>
       </c>
       <c r="G14">
-        <v>-11.00200666278459</v>
+        <v>-8.626339320530356</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>1.443176400450507</v>
       </c>
       <c r="E15">
-        <v>-29.44480576025939</v>
+        <v>-26.29566417905936</v>
       </c>
       <c r="F15">
-        <v>-0.3660026870308301</v>
+        <v>0.1684790137056753</v>
       </c>
       <c r="G15">
-        <v>-9.985268606218089</v>
+        <v>-8.521054040744913</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>1.765376478147737</v>
       </c>
       <c r="E16">
-        <v>-28.83020579641238</v>
+        <v>-27.90287847454367</v>
       </c>
       <c r="F16">
-        <v>-0.5242863019903569</v>
+        <v>0.3361488597063232</v>
       </c>
       <c r="G16">
-        <v>-10.04675867906451</v>
+        <v>-7.34123188982283</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>2.06283408213364</v>
       </c>
       <c r="E17">
-        <v>-30.6539807758915</v>
+        <v>-28.13082827066777</v>
       </c>
       <c r="F17">
-        <v>-0.08741113232571718</v>
+        <v>0.3825258371194564</v>
       </c>
       <c r="G17">
-        <v>-8.371569667464662</v>
+        <v>-7.677037076598803</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>2.334679529120258</v>
       </c>
       <c r="E18">
-        <v>-30.5896266317685</v>
+        <v>-30.61822168088993</v>
       </c>
       <c r="F18">
-        <v>0.08224431033944116</v>
+        <v>0.9410558719266342</v>
       </c>
       <c r="G18">
-        <v>-8.605664963637606</v>
+        <v>-7.138361659176292</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>2.587152752978348</v>
       </c>
       <c r="E19">
-        <v>-32.30337327828325</v>
+        <v>-30.72597671990245</v>
       </c>
       <c r="F19">
-        <v>0.5047539325047318</v>
+        <v>0.9737034880057683</v>
       </c>
       <c r="G19">
-        <v>-7.556274996417269</v>
+        <v>-6.609511940914337</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>2.823567304838568</v>
       </c>
       <c r="E20">
-        <v>-32.44138984485203</v>
+        <v>-30.34207307166519</v>
       </c>
       <c r="F20">
-        <v>0.4849045927988501</v>
+        <v>0.9608356287706808</v>
       </c>
       <c r="G20">
-        <v>-8.070137875022942</v>
+        <v>-5.791131841424343</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>3.053268623502816</v>
       </c>
       <c r="E21">
-        <v>-33.59308041143077</v>
+        <v>-31.47005481257677</v>
       </c>
       <c r="F21">
-        <v>0.6661083054264363</v>
+        <v>1.263902126758908</v>
       </c>
       <c r="G21">
-        <v>-7.599838465168538</v>
+        <v>-5.743698344937665</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>3.282444419252579</v>
       </c>
       <c r="E22">
-        <v>-33.4437336028948</v>
+        <v>-32.56546776842519</v>
       </c>
       <c r="F22">
-        <v>0.8933104315640763</v>
+        <v>1.83411545541517</v>
       </c>
       <c r="G22">
-        <v>-7.472749932461457</v>
+        <v>-5.75902948133003</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>3.514057527015468</v>
       </c>
       <c r="E23">
-        <v>-34.11898794760055</v>
+        <v>-33.12402786642728</v>
       </c>
       <c r="F23">
-        <v>0.7818221195560965</v>
+        <v>1.800858160927576</v>
       </c>
       <c r="G23">
-        <v>-7.331396259025655</v>
+        <v>-5.298698124094372</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>3.755032695796638</v>
       </c>
       <c r="E24">
-        <v>-34.30597996056228</v>
+        <v>-32.90790191593721</v>
       </c>
       <c r="F24">
-        <v>1.25187754553987</v>
+        <v>2.001820092846736</v>
       </c>
       <c r="G24">
-        <v>-7.522272383183414</v>
+        <v>-5.581412092057052</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>4.001391884397632</v>
       </c>
       <c r="E25">
-        <v>-33.98272163623574</v>
+        <v>-33.74338046374535</v>
       </c>
       <c r="F25">
-        <v>1.036576573878251</v>
+        <v>1.830556789052743</v>
       </c>
       <c r="G25">
-        <v>-6.951514468939826</v>
+        <v>-5.0845290015223</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>4.255995869699466</v>
       </c>
       <c r="E26">
-        <v>-34.75712012662842</v>
+        <v>-33.71740740107435</v>
       </c>
       <c r="F26">
-        <v>0.8515143258884245</v>
+        <v>1.762890769387663</v>
       </c>
       <c r="G26">
-        <v>-7.957016533946046</v>
+        <v>-5.597282847372319</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>4.512928308295821</v>
       </c>
       <c r="E27">
-        <v>-34.53257347872108</v>
+        <v>-33.73153623997828</v>
       </c>
       <c r="F27">
-        <v>0.8382157156038812</v>
+        <v>1.860220625746994</v>
       </c>
       <c r="G27">
-        <v>-7.88273120259034</v>
+        <v>-5.598328979762728</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>4.761946359737211</v>
       </c>
       <c r="E28">
-        <v>-34.44156700082594</v>
+        <v>-33.24779785376793</v>
       </c>
       <c r="F28">
-        <v>1.181287388942908</v>
+        <v>2.162326217547973</v>
       </c>
       <c r="G28">
-        <v>-7.029246078201913</v>
+        <v>-5.310142680023632</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>4.993821210322962</v>
       </c>
       <c r="E29">
-        <v>-35.2496052603846</v>
+        <v>-33.36804015985659</v>
       </c>
       <c r="F29">
-        <v>1.245091559776137</v>
+        <v>1.870015241917695</v>
       </c>
       <c r="G29">
-        <v>-8.174151905321304</v>
+        <v>-5.580945305136015</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>5.188245417273063</v>
       </c>
       <c r="E30">
-        <v>-34.036010454121</v>
+        <v>-33.56992179535554</v>
       </c>
       <c r="F30">
-        <v>0.6282444598118737</v>
+        <v>1.932379710204859</v>
       </c>
       <c r="G30">
-        <v>-7.995031528373497</v>
+        <v>-6.322841871032227</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>5.334137939722862</v>
       </c>
       <c r="E31">
-        <v>-34.34189755215412</v>
+        <v>-32.51515189372596</v>
       </c>
       <c r="F31">
-        <v>0.5611732079420033</v>
+        <v>1.801913500998742</v>
       </c>
       <c r="G31">
-        <v>-8.368745772119665</v>
+        <v>-6.378303440451638</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>5.415542640714617</v>
       </c>
       <c r="E32">
-        <v>-33.81188948277039</v>
+        <v>-32.438425958614</v>
       </c>
       <c r="F32">
-        <v>0.5002136507699877</v>
+        <v>1.802929079434574</v>
       </c>
       <c r="G32">
-        <v>-8.162465679567676</v>
+        <v>-6.446590063290184</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>5.42058261898452</v>
       </c>
       <c r="E33">
-        <v>-33.68808100340068</v>
+        <v>-32.65655575885248</v>
       </c>
       <c r="F33">
-        <v>0.5320163320982664</v>
+        <v>1.672399914305845</v>
       </c>
       <c r="G33">
-        <v>-7.7027567048934</v>
+        <v>-6.332283546910229</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>5.344450366701131</v>
       </c>
       <c r="E34">
-        <v>-32.50589342861728</v>
+        <v>-33.09095189227526</v>
       </c>
       <c r="F34">
-        <v>0.595892570895539</v>
+        <v>1.716715913620813</v>
       </c>
       <c r="G34">
-        <v>-8.413474552900757</v>
+        <v>-6.46146434439813</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>5.181379099964127</v>
       </c>
       <c r="E35">
-        <v>-31.64538600496875</v>
+        <v>-30.9998293928053</v>
       </c>
       <c r="F35">
-        <v>0.7948722196197998</v>
+        <v>1.725620863200908</v>
       </c>
       <c r="G35">
-        <v>-8.945280588329281</v>
+        <v>-6.315211063564208</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>4.93703436787789</v>
       </c>
       <c r="E36">
-        <v>-30.91117998563115</v>
+        <v>-31.54529993668822</v>
       </c>
       <c r="F36">
-        <v>0.645116647072094</v>
+        <v>1.8047713685384</v>
       </c>
       <c r="G36">
-        <v>-8.885419303888179</v>
+        <v>-6.522457835413662</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>4.614943613571135</v>
       </c>
       <c r="E37">
-        <v>-31.59285117800577</v>
+        <v>-29.92319375442969</v>
       </c>
       <c r="F37">
-        <v>1.075524752423078</v>
+        <v>1.789481363017527</v>
       </c>
       <c r="G37">
-        <v>-8.690736052360258</v>
+        <v>-7.443636994989106</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>4.222697352263781</v>
       </c>
       <c r="E38">
-        <v>-30.65308640227499</v>
+        <v>-29.69215327479535</v>
       </c>
       <c r="F38">
-        <v>0.8857888555466568</v>
+        <v>1.611844600426396</v>
       </c>
       <c r="G38">
-        <v>-8.709904111032639</v>
+        <v>-6.494973686346633</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>3.770456929711894</v>
       </c>
       <c r="E39">
-        <v>-30.4506500287101</v>
+        <v>-29.23266486689607</v>
       </c>
       <c r="F39">
-        <v>0.470241661401896</v>
+        <v>1.650338833634488</v>
       </c>
       <c r="G39">
-        <v>-8.471068113647458</v>
+        <v>-6.775585457891877</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>3.265630991995218</v>
       </c>
       <c r="E40">
-        <v>-29.36596955625986</v>
+        <v>-28.85765740584688</v>
       </c>
       <c r="F40">
-        <v>0.5706066559250841</v>
+        <v>1.263718229195486</v>
       </c>
       <c r="G40">
-        <v>-9.813702894190898</v>
+        <v>-7.089166952462722</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>2.721975577754184</v>
       </c>
       <c r="E41">
-        <v>-29.04248254399594</v>
+        <v>-29.17278938356665</v>
       </c>
       <c r="F41">
-        <v>0.8280334234886697</v>
+        <v>1.677918497943295</v>
       </c>
       <c r="G41">
-        <v>-9.255392631174969</v>
+        <v>-6.332750333831267</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>2.149485700850585</v>
       </c>
       <c r="E42">
-        <v>-28.92185305337961</v>
+        <v>-26.90437259822239</v>
       </c>
       <c r="F42">
-        <v>1.020728248727891</v>
+        <v>1.523923341028061</v>
       </c>
       <c r="G42">
-        <v>-9.042031281714481</v>
+        <v>-7.497105615993875</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>1.560342601158055</v>
       </c>
       <c r="E43">
-        <v>-28.22862519533742</v>
+        <v>-27.61079642952294</v>
       </c>
       <c r="F43">
-        <v>0.7371184442966183</v>
+        <v>1.715889202952819</v>
       </c>
       <c r="G43">
-        <v>-10.83346016828922</v>
+        <v>-6.473382308339506</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>0.9665399431917064</v>
       </c>
       <c r="E44">
-        <v>-26.88816971822295</v>
+        <v>-26.41417434384009</v>
       </c>
       <c r="F44">
-        <v>0.6995478407426468</v>
+        <v>1.877929464084041</v>
       </c>
       <c r="G44">
-        <v>-10.26609225267785</v>
+        <v>-7.077335062705367</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>0.3765480917346998</v>
       </c>
       <c r="E45">
-        <v>-27.08723690712613</v>
+        <v>-26.85421974858744</v>
       </c>
       <c r="F45">
-        <v>0.9159132645168636</v>
+        <v>1.702053810591262</v>
       </c>
       <c r="G45">
-        <v>-9.536030887084527</v>
+        <v>-7.609710511966645</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-0.1975679357406279</v>
       </c>
       <c r="E46">
-        <v>-25.79907624785223</v>
+        <v>-26.36979982703893</v>
       </c>
       <c r="F46">
-        <v>1.174556075427759</v>
+        <v>1.911776556162429</v>
       </c>
       <c r="G46">
-        <v>-9.93869916211716</v>
+        <v>-7.602668981604615</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-0.7472302293427321</v>
       </c>
       <c r="E47">
-        <v>-25.3405591976276</v>
+        <v>-25.50797688169117</v>
       </c>
       <c r="F47">
-        <v>0.738685715422715</v>
+        <v>1.981110907776748</v>
       </c>
       <c r="G47">
-        <v>-10.87393158750681</v>
+        <v>-8.17576083045339</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.264441702819912</v>
       </c>
       <c r="E48">
-        <v>-25.20033952845409</v>
+        <v>-24.74813969947015</v>
       </c>
       <c r="F48">
-        <v>0.7033856669198169</v>
+        <v>1.643950464224099</v>
       </c>
       <c r="G48">
-        <v>-10.02983517026776</v>
+        <v>-7.654627993843476</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.743097724263817</v>
       </c>
       <c r="E49">
-        <v>-24.99735973800828</v>
+        <v>-24.39328394775509</v>
       </c>
       <c r="F49">
-        <v>1.146613586196526</v>
+        <v>1.659634772628705</v>
       </c>
       <c r="G49">
-        <v>-10.55693360993944</v>
+        <v>-7.697499558577038</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.17948676447477</v>
       </c>
       <c r="E50">
-        <v>-23.69351697324582</v>
+        <v>-24.08603151480867</v>
       </c>
       <c r="F50">
-        <v>0.993074031352832</v>
+        <v>1.688780051328802</v>
       </c>
       <c r="G50">
-        <v>-10.80482063882899</v>
+        <v>-7.350368995511219</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.571530700153067</v>
       </c>
       <c r="E51">
-        <v>-24.51946534750482</v>
+        <v>-22.14907638445584</v>
       </c>
       <c r="F51">
-        <v>0.6011071436961619</v>
+        <v>1.837634360142262</v>
       </c>
       <c r="G51">
-        <v>-11.66843603256758</v>
+        <v>-7.902478606732092</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.917610745272073</v>
       </c>
       <c r="E52">
-        <v>-23.31659396769139</v>
+        <v>-22.3847925135031</v>
       </c>
       <c r="F52">
-        <v>0.7366048565068827</v>
+        <v>1.723482018566879</v>
       </c>
       <c r="G52">
-        <v>-11.00971361280002</v>
+        <v>-7.731131390710494</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-3.219947240906507</v>
       </c>
       <c r="E53">
-        <v>-22.66550356029057</v>
+        <v>-21.51815580028519</v>
       </c>
       <c r="F53">
-        <v>1.0149313336431</v>
+        <v>1.83719863888839</v>
       </c>
       <c r="G53">
-        <v>-10.99154202833496</v>
+        <v>-8.16435931161614</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-3.480737756160095</v>
       </c>
       <c r="E54">
-        <v>-22.28524306939248</v>
+        <v>-21.94065789672682</v>
       </c>
       <c r="F54">
-        <v>0.5733162456996412</v>
+        <v>2.084572339651601</v>
       </c>
       <c r="G54">
-        <v>-10.40471141549821</v>
+        <v>-8.250718202553568</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-3.701343283597611</v>
       </c>
       <c r="E55">
-        <v>-22.22181726244105</v>
+        <v>-20.38109673322523</v>
       </c>
       <c r="F55">
-        <v>0.5849084191344176</v>
+        <v>1.16568260380897</v>
       </c>
       <c r="G55">
-        <v>-11.49429802665638</v>
+        <v>-8.082648426615847</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-3.887070870543389</v>
       </c>
       <c r="E56">
-        <v>-21.29768251474774</v>
+        <v>-20.5506971417605</v>
       </c>
       <c r="F56">
-        <v>0.4036276683383709</v>
+        <v>1.18509622226098</v>
       </c>
       <c r="G56">
-        <v>-11.00654542071894</v>
+        <v>-8.406625034180005</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-4.037779042998009</v>
       </c>
       <c r="E57">
-        <v>-20.92608952310034</v>
+        <v>-19.41794012500783</v>
       </c>
       <c r="F57">
-        <v>0.426347301094953</v>
+        <v>1.681868153719843</v>
       </c>
       <c r="G57">
-        <v>-11.51085075435273</v>
+        <v>-8.903564403988923</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-4.159745851402806</v>
       </c>
       <c r="E58">
-        <v>-20.62650832512291</v>
+        <v>-19.07570975882615</v>
       </c>
       <c r="F58">
-        <v>0.442126043383478</v>
+        <v>1.192955772178741</v>
       </c>
       <c r="G58">
-        <v>-11.58881079125703</v>
+        <v>-8.853740693622893</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-4.255064807102343</v>
       </c>
       <c r="E59">
-        <v>-20.12630214318365</v>
+        <v>-18.52778251779407</v>
       </c>
       <c r="F59">
-        <v>0.2177006047800219</v>
+        <v>1.044093179691254</v>
       </c>
       <c r="G59">
-        <v>-11.73388882842451</v>
+        <v>-8.630874767919156</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.324257552654727</v>
       </c>
       <c r="E60">
-        <v>-19.24383388483492</v>
+        <v>-18.87322810052119</v>
       </c>
       <c r="F60">
-        <v>0.5300141680856999</v>
+        <v>1.240149519851035</v>
       </c>
       <c r="G60">
-        <v>-11.40018583806598</v>
+        <v>-9.101826355244798</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.372753367798534</v>
       </c>
       <c r="E61">
-        <v>-19.74595108280541</v>
+        <v>-18.49914897664357</v>
       </c>
       <c r="F61">
-        <v>0.1343809263042393</v>
+        <v>1.172100794445861</v>
       </c>
       <c r="G61">
-        <v>-10.57187410195817</v>
+        <v>-8.684161308919265</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-4.396939616259584</v>
       </c>
       <c r="E62">
-        <v>-19.3829169070325</v>
+        <v>-17.64261981741078</v>
       </c>
       <c r="F62">
-        <v>0.03128231935181278</v>
+        <v>1.096197489327343</v>
       </c>
       <c r="G62">
-        <v>-11.59885167587764</v>
+        <v>-9.432622686619853</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-4.402476674211323</v>
       </c>
       <c r="E63">
-        <v>-17.9200567774907</v>
+        <v>-17.84996505679998</v>
       </c>
       <c r="F63">
-        <v>0.2258417996147355</v>
+        <v>1.30865716079736</v>
       </c>
       <c r="G63">
-        <v>-11.59655746781893</v>
+        <v>-9.430563527294426</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-4.388871906773781</v>
       </c>
       <c r="E64">
-        <v>-18.02715518777211</v>
+        <v>-17.02076070972947</v>
       </c>
       <c r="F64">
-        <v>0.1985553773665197</v>
+        <v>0.7438845492426847</v>
       </c>
       <c r="G64">
-        <v>-11.6038638418241</v>
+        <v>-9.48596219634859</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-4.355827842209819</v>
       </c>
       <c r="E65">
-        <v>-18.32950781184223</v>
+        <v>-17.32767350712532</v>
       </c>
       <c r="F65">
-        <v>-0.2107359861522992</v>
+        <v>1.048756888169015</v>
       </c>
       <c r="G65">
-        <v>-12.442299226191</v>
+        <v>-9.094467012510997</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-4.306995611381994</v>
       </c>
       <c r="E66">
-        <v>-17.66380401881866</v>
+        <v>-16.5712598512541</v>
       </c>
       <c r="F66">
-        <v>-0.0495141520150426</v>
+        <v>0.7179019772864754</v>
       </c>
       <c r="G66">
-        <v>-12.08719024837553</v>
+        <v>-9.376972416104705</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-4.237439837674703</v>
       </c>
       <c r="E67">
-        <v>-18.06591892527776</v>
+        <v>-17.8147878707084</v>
       </c>
       <c r="F67">
-        <v>0.064421157300807</v>
+        <v>0.8769501753587861</v>
       </c>
       <c r="G67">
-        <v>-12.11182732827879</v>
+        <v>-10.85377698626373</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-4.152070116158583</v>
       </c>
       <c r="E68">
-        <v>-17.48705314982528</v>
+        <v>-16.61525397623862</v>
       </c>
       <c r="F68">
-        <v>-0.4432512608114952</v>
+        <v>0.5848711426012916</v>
       </c>
       <c r="G68">
-        <v>-12.55075269805752</v>
+        <v>-9.578031778341261</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-4.048393756349623</v>
       </c>
       <c r="E69">
-        <v>-17.91138474976601</v>
+        <v>-16.38359988837624</v>
       </c>
       <c r="F69">
-        <v>-0.2181001723631868</v>
+        <v>0.7297376907376747</v>
       </c>
       <c r="G69">
-        <v>-11.61422253881648</v>
+        <v>-10.33421996933051</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-3.925767077762529</v>
       </c>
       <c r="E70">
-        <v>-17.50528931465417</v>
+        <v>-16.55194138113738</v>
       </c>
       <c r="F70">
-        <v>0.09954062170989483</v>
+        <v>0.4221524485671763</v>
       </c>
       <c r="G70">
-        <v>-11.24887073310251</v>
+        <v>-10.17823368461113</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-3.78587607998653</v>
       </c>
       <c r="E71">
-        <v>-17.33129628633145</v>
+        <v>-17.35490322133344</v>
       </c>
       <c r="F71">
-        <v>-0.1712129206299292</v>
+        <v>0.3579995350573686</v>
       </c>
       <c r="G71">
-        <v>-12.16332286414215</v>
+        <v>-10.17441662560435</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-3.623833890185958</v>
       </c>
       <c r="E72">
-        <v>-17.91932316470146</v>
+        <v>-17.43172878287357</v>
       </c>
       <c r="F72">
-        <v>-0.2935743831670554</v>
+        <v>0.42261219247573</v>
       </c>
       <c r="G72">
-        <v>-11.26835329360112</v>
+        <v>-9.463718640870226</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-3.443462979473671</v>
       </c>
       <c r="E73">
-        <v>-17.65094768111088</v>
+        <v>-16.64909526249794</v>
       </c>
       <c r="F73">
-        <v>-0.2787118152260266</v>
+        <v>0.2924276281865653</v>
       </c>
       <c r="G73">
-        <v>-11.77370807017087</v>
+        <v>-9.837290531158205</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-3.242143670716453</v>
       </c>
       <c r="E74">
-        <v>-17.1590467205017</v>
+        <v>-17.02583712909207</v>
       </c>
       <c r="F74">
-        <v>-0.3103827861372601</v>
+        <v>0.2317364620530567</v>
       </c>
       <c r="G74">
-        <v>-11.78474542899879</v>
+        <v>-9.99448516499942</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-3.02062954559344</v>
       </c>
       <c r="E75">
-        <v>-16.74422944445108</v>
+        <v>-17.07981201078949</v>
       </c>
       <c r="F75">
-        <v>-0.1645528467114211</v>
+        <v>-0.07998481855961961</v>
       </c>
       <c r="G75">
-        <v>-11.0088859764152</v>
+        <v>-9.663933813994269</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-2.780712417999113</v>
       </c>
       <c r="E76">
-        <v>-18.05668989525013</v>
+        <v>-16.86792018349659</v>
       </c>
       <c r="F76">
-        <v>-0.6237400923704655</v>
+        <v>-0.2058320511277261</v>
       </c>
       <c r="G76">
-        <v>-10.82200568072334</v>
+        <v>-10.09880376548739</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-2.520067250312923</v>
       </c>
       <c r="E77">
-        <v>-18.11116743756241</v>
+        <v>-17.62145825837293</v>
       </c>
       <c r="F77">
-        <v>-0.3618699620582634</v>
+        <v>0.2411914475886103</v>
       </c>
       <c r="G77">
-        <v>-10.49110672243657</v>
+        <v>-9.930445972087757</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-2.242378811375208</v>
       </c>
       <c r="E78">
-        <v>-19.17278665612858</v>
+        <v>-17.63694563947917</v>
       </c>
       <c r="F78">
-        <v>-0.4556328683811394</v>
+        <v>0.2475773318967917</v>
       </c>
       <c r="G78">
-        <v>-9.444951158208099</v>
+        <v>-9.381842228592973</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-1.946274332811635</v>
       </c>
       <c r="E79">
-        <v>-19.39794691226396</v>
+        <v>-19.11876196121707</v>
       </c>
       <c r="F79">
-        <v>-0.8189523261467941</v>
+        <v>0.1022899731197864</v>
       </c>
       <c r="G79">
-        <v>-10.25814032229252</v>
+        <v>-9.141248331526439</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-1.632776496982279</v>
       </c>
       <c r="E80">
-        <v>-19.44983869591785</v>
+        <v>-19.20914577393617</v>
       </c>
       <c r="F80">
-        <v>-0.6745355815101312</v>
+        <v>-0.09403807154811322</v>
       </c>
       <c r="G80">
-        <v>-9.795028106803869</v>
+        <v>-8.083936228830625</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-1.3024711284668</v>
       </c>
       <c r="E81">
-        <v>-19.36903260572499</v>
+        <v>-20.09513265658886</v>
       </c>
       <c r="F81">
-        <v>-0.6330675093259879</v>
+        <v>-0.1434824934538129</v>
       </c>
       <c r="G81">
-        <v>-9.487604226936069</v>
+        <v>-7.980355879997908</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-0.9546126321213745</v>
       </c>
       <c r="E82">
-        <v>-21.96791025330498</v>
+        <v>-20.37804001327005</v>
       </c>
       <c r="F82">
-        <v>-0.8063304920303381</v>
+        <v>-0.1900400549607563</v>
       </c>
       <c r="G82">
-        <v>-8.960178043256001</v>
+        <v>-7.696046229085298</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-0.5921308368403513</v>
       </c>
       <c r="E83">
-        <v>-22.65948974680838</v>
+        <v>-21.11222791871162</v>
       </c>
       <c r="F83">
-        <v>-0.859455350306676</v>
+        <v>-0.21131915680387</v>
       </c>
       <c r="G83">
-        <v>-8.736765877538284</v>
+        <v>-7.861540400593465</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-0.2166227635847172</v>
       </c>
       <c r="E84">
-        <v>-22.71968222331834</v>
+        <v>-21.58994117025478</v>
       </c>
       <c r="F84">
-        <v>-0.5036549834562324</v>
+        <v>-0.5436783828898932</v>
       </c>
       <c r="G84">
-        <v>-8.295559541882996</v>
+        <v>-7.114333719652262</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>0.16742811235976</v>
       </c>
       <c r="E85">
-        <v>-23.5074102769526</v>
+        <v>-22.79368201707768</v>
       </c>
       <c r="F85">
-        <v>-0.9578968757205637</v>
+        <v>-0.3863316514629328</v>
       </c>
       <c r="G85">
-        <v>-8.499899654748971</v>
+        <v>-7.707715902111229</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>0.5537664829319884</v>
       </c>
       <c r="E86">
-        <v>-24.70578488207641</v>
+        <v>-24.76675172764168</v>
       </c>
       <c r="F86">
-        <v>-0.7430465359260671</v>
+        <v>-0.1949174822284398</v>
       </c>
       <c r="G86">
-        <v>-8.669459176179362</v>
+        <v>-6.329701321389598</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>0.9346380100201543</v>
       </c>
       <c r="E87">
-        <v>-25.90276018873185</v>
+        <v>-25.13229920648884</v>
       </c>
       <c r="F87">
-        <v>-1.269134389770005</v>
+        <v>-0.3740883812495561</v>
       </c>
       <c r="G87">
-        <v>-7.979601075614954</v>
+        <v>-6.401771897779531</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>1.299199769637087</v>
       </c>
       <c r="E88">
-        <v>-27.61238592389963</v>
+        <v>-27.05269823586963</v>
       </c>
       <c r="F88">
-        <v>-1.066891801846117</v>
+        <v>-0.5920169343128556</v>
       </c>
       <c r="G88">
-        <v>-7.711033068741579</v>
+        <v>-6.537126862698173</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>1.635842825655754</v>
       </c>
       <c r="E89">
-        <v>-28.56120085493474</v>
+        <v>-28.64396324589892</v>
       </c>
       <c r="F89">
-        <v>-1.077409582759462</v>
+        <v>-0.5185407456845395</v>
       </c>
       <c r="G89">
-        <v>-7.1251525824746</v>
+        <v>-6.506838681559381</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>1.931157299827443</v>
       </c>
       <c r="E90">
-        <v>-29.72043812344726</v>
+        <v>-30.36921448063016</v>
       </c>
       <c r="F90">
-        <v>-1.286969139952278</v>
+        <v>-0.803910002479358</v>
       </c>
       <c r="G90">
-        <v>-7.330399784818335</v>
+        <v>-6.289769521094908</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>2.171798389622017</v>
       </c>
       <c r="E91">
-        <v>-31.17429111818781</v>
+        <v>-31.62913557599223</v>
       </c>
       <c r="F91">
-        <v>-1.429478154460294</v>
+        <v>-0.7237961058524094</v>
       </c>
       <c r="G91">
-        <v>-7.812249688059256</v>
+        <v>-6.72546710897285</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>2.345311554005415</v>
       </c>
       <c r="E92">
-        <v>-32.86356815540211</v>
+        <v>-33.82509904145076</v>
       </c>
       <c r="F92">
-        <v>-1.371502376673162</v>
+        <v>-0.7185831897865921</v>
       </c>
       <c r="G92">
-        <v>-8.100277081612466</v>
+        <v>-6.672034903969013</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>2.438814178517608</v>
       </c>
       <c r="E93">
-        <v>-35.54024498643388</v>
+        <v>-34.82044404291468</v>
       </c>
       <c r="F93">
-        <v>-1.545466158200281</v>
+        <v>-0.7496361986153371</v>
       </c>
       <c r="G93">
-        <v>-8.3597708831627</v>
+        <v>-6.544257777789763</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>2.443068228081652</v>
       </c>
       <c r="E94">
-        <v>-37.58272714658746</v>
+        <v>-37.15524825721139</v>
       </c>
       <c r="F94">
-        <v>-1.542162628997916</v>
+        <v>-0.9997228026227163</v>
       </c>
       <c r="G94">
-        <v>-7.500584999355649</v>
+        <v>-6.307153195721622</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>2.35218109587934</v>
       </c>
       <c r="E95">
-        <v>-38.25588254359065</v>
+        <v>-39.46125364105632</v>
       </c>
       <c r="F95">
-        <v>-1.950713432058633</v>
+        <v>-1.122013025563202</v>
       </c>
       <c r="G95">
-        <v>-8.383149955761033</v>
+        <v>-6.470459096628329</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>2.156643392735686</v>
       </c>
       <c r="E96">
-        <v>-42.30311108999187</v>
+        <v>-41.11847134653332</v>
       </c>
       <c r="F96">
-        <v>-1.969654881091046</v>
+        <v>-0.9806057397009094</v>
       </c>
       <c r="G96">
-        <v>-8.652562151746922</v>
+        <v>-6.949885680534504</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>1.865838114854904</v>
       </c>
       <c r="E97">
-        <v>-43.27895195390476</v>
+        <v>-43.29815947640829</v>
       </c>
       <c r="F97">
-        <v>-2.284249768224034</v>
+        <v>-1.150976063434684</v>
       </c>
       <c r="G97">
-        <v>-8.113294146672882</v>
+        <v>-7.638691027617424</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>1.466677765555712</v>
       </c>
       <c r="E98">
-        <v>-45.44205228348963</v>
+        <v>-46.07228453961112</v>
       </c>
       <c r="F98">
-        <v>-2.402997063782746</v>
+        <v>-1.233206438775785</v>
       </c>
       <c r="G98">
-        <v>-8.291096926496058</v>
+        <v>-7.431576677589541</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>0.9931160646111404</v>
       </c>
       <c r="E99">
-        <v>-48.39037868481952</v>
+        <v>-48.48896582820351</v>
       </c>
       <c r="F99">
-        <v>-2.676819707349942</v>
+        <v>-1.571524111590145</v>
       </c>
       <c r="G99">
-        <v>-8.654743801257302</v>
+        <v>-8.050546066521536</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>0.4145728034603786</v>
       </c>
       <c r="E100">
-        <v>-50.08515102524214</v>
+        <v>-51.12289386460287</v>
       </c>
       <c r="F100">
-        <v>-2.867357463872273</v>
+        <v>-1.971377885288869</v>
       </c>
       <c r="G100">
-        <v>-9.270392713013408</v>
+        <v>-8.038952536043007</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-0.191825372372831</v>
       </c>
       <c r="E101">
-        <v>-52.94104108300896</v>
+        <v>-52.73639821048384</v>
       </c>
       <c r="F101">
-        <v>-3.141209100298568</v>
+        <v>-1.597108238825608</v>
       </c>
       <c r="G101">
-        <v>-9.532495224448585</v>
+        <v>-8.988622250529419</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-0.9265094142447617</v>
       </c>
       <c r="E102">
-        <v>-54.79547722787552</v>
+        <v>-55.54785035281339</v>
       </c>
       <c r="F102">
-        <v>-3.253760207684339</v>
+        <v>-1.912971356452282</v>
       </c>
       <c r="G102">
-        <v>-9.755414118880951</v>
+        <v>-9.419837359747188</v>
       </c>
     </row>
   </sheetData>
